--- a/Assets/Resources/Data/Excels/CardData.xlsx
+++ b/Assets/Resources/Data/Excels/CardData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\My project\Assets\Resources\Data\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\YMAMiniGames\YMAMinigame\Assets\Resources\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA40E4DD-027E-456A-A16D-05E3B8B5C1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5331ED99-1494-4266-86A7-2009F2979FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="42450" yWindow="3750" windowWidth="31935" windowHeight="18660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="66">
   <si>
     <t>number</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -265,6 +265,22 @@
   </si>
   <si>
     <t>#91</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#82</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -469,7 +485,17 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="60">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -492,6 +518,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -507,16 +563,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -544,6 +590,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -554,6 +610,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -569,16 +655,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -596,6 +672,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -606,6 +692,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -621,16 +737,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -658,6 +764,46 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -673,16 +819,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -730,11 +866,31 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -750,8 +906,211 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF9C0006"/>
+      <color rgb="FFFFC7CE"/>
+      <color rgb="FFFBE2D5"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1649,8 +2008,8 @@
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="7">
-        <v>18</v>
+      <c r="A20" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>27</v>
@@ -1691,10 +2050,10 @@
       <c r="E21" s="4">
         <v>2000</v>
       </c>
-      <c r="N21" s="4" t="s">
+      <c r="N21" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="O21" s="4">
+      <c r="O21" s="10">
         <v>19</v>
       </c>
       <c r="P21" s="9">
@@ -1703,8 +2062,8 @@
       </c>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="7">
-        <v>20</v>
+      <c r="A22" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>29</v>
@@ -1745,10 +2104,10 @@
       <c r="E23" s="4">
         <v>2200</v>
       </c>
-      <c r="N23" s="4" t="s">
+      <c r="N23" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="O23" s="4">
+      <c r="O23" s="10">
         <v>21</v>
       </c>
       <c r="P23" s="9">
@@ -1838,8 +2197,8 @@
       </c>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="7">
-        <v>25</v>
+      <c r="A27" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>34</v>
@@ -1880,10 +2239,10 @@
       <c r="E28" s="4">
         <v>2700</v>
       </c>
-      <c r="N28" s="4" t="s">
+      <c r="N28" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="O28" s="4">
+      <c r="O28" s="10">
         <v>26</v>
       </c>
       <c r="P28" s="9">
@@ -2910,8 +3269,8 @@
       </c>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="7">
-        <v>82</v>
+      <c r="A84" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>29</v>
@@ -3425,23 +3784,32 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="#">
+    <cfRule type="containsText" dxfId="8" priority="14" operator="containsText" text="#">
       <formula>NOT(ISERROR(SEARCH("#",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+      <formula>$N$5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="13" operator="equal">
+      <formula>$J$1</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>$N$25</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
-      <formula>$J$1</formula>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>$N$21</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
-      <formula>$N$5</formula>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>$N$23</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+      <formula>$N$28</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1" xr:uid="{A5C6619D-5FF7-4FBD-A4F0-111C82B23071}">
@@ -3454,7 +3822,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="11" operator="containsText" id="{6013EFDF-943F-4BD5-8F74-030CA517C5B7}">
+          <x14:cfRule type="containsText" priority="8" operator="containsText" id="{6013EFDF-943F-4BD5-8F74-030CA517C5B7}">
             <xm:f>NOT(ISERROR(SEARCH($N$33,B1)))</xm:f>
             <xm:f>$N$33</xm:f>
             <x14:dxf>
